--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134433703</v>
+        <v>135506024</v>
       </c>
       <c r="B3" t="n">
-        <v>98066</v>
+        <v>106199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,41 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221154</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, SSO om, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481167</v>
+        <v>481186</v>
       </c>
       <c r="R3" t="n">
-        <v>6596341</v>
+        <v>6596385</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,23 +878,28 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134433704</v>
+        <v>134433703</v>
       </c>
       <c r="B4" t="n">
         <v>98066</v>
@@ -952,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481132</v>
+        <v>481167</v>
       </c>
       <c r="R4" t="n">
-        <v>6596362</v>
+        <v>6596341</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134433706</v>
+        <v>134433704</v>
       </c>
       <c r="B5" t="n">
         <v>98066</v>
@@ -1068,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481138</v>
+        <v>481132</v>
       </c>
       <c r="R5" t="n">
-        <v>6596301</v>
+        <v>6596362</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1145,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134433707</v>
+        <v>134433706</v>
       </c>
       <c r="B6" t="n">
         <v>98066</v>
@@ -1184,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481133</v>
+        <v>481138</v>
       </c>
       <c r="R6" t="n">
-        <v>6596304</v>
+        <v>6596301</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1261,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134433709</v>
+        <v>134433707</v>
       </c>
       <c r="B7" t="n">
-        <v>98063</v>
+        <v>98066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,16 +1258,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1300,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481166</v>
+        <v>481133</v>
       </c>
       <c r="R7" t="n">
-        <v>6596345</v>
+        <v>6596304</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1377,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134433711</v>
+        <v>135506022</v>
       </c>
       <c r="B8" t="n">
-        <v>98063</v>
+        <v>98066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,16 +1374,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1405,24 +1391,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, S om, skjutbana, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481132</v>
+        <v>481140</v>
       </c>
       <c r="R8" t="n">
-        <v>6596358</v>
+        <v>6596332</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,27 +1428,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Längs stigen mot skjutvallen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,23 +1449,28 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134433712</v>
+        <v>134433709</v>
       </c>
       <c r="B9" t="n">
         <v>98063</v>
@@ -1532,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481131</v>
+        <v>481166</v>
       </c>
       <c r="R9" t="n">
-        <v>6596311</v>
+        <v>6596345</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1567,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1606,6 +1583,336 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134433711</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481132</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6596358</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134433712</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6596311</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135506027</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98064</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillsjön, SSO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481186</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6596385</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130798963</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433704</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433706</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433707</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433709</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1699,6 +1744,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433711</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1815,6 +1865,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433712</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,8 +1968,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>135506024</v>
       </c>
       <c r="B3" t="n">
-        <v>106199</v>
+        <v>106254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135506022</v>
       </c>
       <c r="B8" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>135506027</v>
       </c>
       <c r="B12" t="n">
-        <v>98064</v>
+        <v>98108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>135506024</v>
       </c>
       <c r="B3" t="n">
-        <v>106254</v>
+        <v>106281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135506022</v>
       </c>
       <c r="B8" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>135506027</v>
       </c>
       <c r="B12" t="n">
-        <v>98108</v>
+        <v>98135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134433703</v>
+        <v>135506024</v>
       </c>
       <c r="B3" t="n">
-        <v>98066</v>
+        <v>106286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,41 +818,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221154</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, SSO om, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481167</v>
+        <v>481186</v>
       </c>
       <c r="R3" t="n">
-        <v>6596341</v>
+        <v>6596385</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,27 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,28 +888,33 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433703</t>
+          <t>https://artportalen.se/Sighting/135506024</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134433704</v>
+        <v>134433703</v>
       </c>
       <c r="B4" t="n">
         <v>98066</v>
@@ -967,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481132</v>
+        <v>481167</v>
       </c>
       <c r="R4" t="n">
-        <v>6596362</v>
+        <v>6596341</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1043,13 +1029,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433704</t>
+          <t>https://artportalen.se/Sighting/134433703</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134433706</v>
+        <v>134433704</v>
       </c>
       <c r="B5" t="n">
         <v>98066</v>
@@ -1088,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481138</v>
+        <v>481132</v>
       </c>
       <c r="R5" t="n">
-        <v>6596301</v>
+        <v>6596362</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1164,13 +1150,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433706</t>
+          <t>https://artportalen.se/Sighting/134433704</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134433707</v>
+        <v>134433706</v>
       </c>
       <c r="B6" t="n">
         <v>98066</v>
@@ -1209,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481133</v>
+        <v>481138</v>
       </c>
       <c r="R6" t="n">
-        <v>6596304</v>
+        <v>6596301</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1285,16 +1271,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433707</t>
+          <t>https://artportalen.se/Sighting/134433706</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134433709</v>
+        <v>134433707</v>
       </c>
       <c r="B7" t="n">
-        <v>98063</v>
+        <v>98066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,16 +1288,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1330,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481166</v>
+        <v>481133</v>
       </c>
       <c r="R7" t="n">
-        <v>6596345</v>
+        <v>6596304</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1365,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1406,16 +1392,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433709</t>
+          <t>https://artportalen.se/Sighting/134433707</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134433711</v>
+        <v>135506022</v>
       </c>
       <c r="B8" t="n">
-        <v>98063</v>
+        <v>98142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,16 +1409,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1440,24 +1426,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, S om, skjutbana, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481132</v>
+        <v>481140</v>
       </c>
       <c r="R8" t="n">
-        <v>6596358</v>
+        <v>6596332</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,27 +1463,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Längs stigen mot skjutvallen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,28 +1484,33 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433711</t>
+          <t>https://artportalen.se/Sighting/135506022</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134433712</v>
+        <v>134433709</v>
       </c>
       <c r="B9" t="n">
         <v>98063</v>
@@ -1572,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481131</v>
+        <v>481166</v>
       </c>
       <c r="R9" t="n">
-        <v>6596311</v>
+        <v>6596345</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1607,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1648,7 +1625,352 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134433709</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134433711</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481132</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6596358</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433711</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134433712</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6596311</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134433712</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135506027</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillsjön, SSO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481186</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6596385</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135506027</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1984,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>135506024</v>
       </c>
       <c r="B3" t="n">
-        <v>106286</v>
+        <v>106288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135506022</v>
       </c>
       <c r="B8" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>135506027</v>
       </c>
       <c r="B12" t="n">
-        <v>98140</v>
+        <v>98142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>135506024</v>
       </c>
       <c r="B3" t="n">
-        <v>106288</v>
+        <v>106308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135506022</v>
       </c>
       <c r="B8" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>135506027</v>
       </c>
       <c r="B12" t="n">
-        <v>98142</v>
+        <v>98159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>135506024</v>
       </c>
       <c r="B3" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135506022</v>
       </c>
       <c r="B8" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>135506027</v>
       </c>
       <c r="B12" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
